--- a/sanaku/docs/sanaku-services.xlsx
+++ b/sanaku/docs/sanaku-services.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Law Firms" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Medical" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Trial" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -105,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,6 +125,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4955,4 +4960,798 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The 30-day trial — cost of the offer, and when it pays back</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Trial: pay the starting fee, run it 30 days, then the monthly begins. Packages are excluded on purpose — a free month of a package is thousands per prospect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Normal setup</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Trial start</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Given up at signup</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Monthly from day 31</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Free month costs</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Year one on trial</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Year one paid up front</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>AI Phone Agent  (home_services)</t>
+        </is>
+      </c>
+      <c r="B5" s="12">
+        <f>'All Services'!E13</f>
+        <v/>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="D5" s="12">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="12">
+        <f>'All Services'!F13</f>
+        <v/>
+      </c>
+      <c r="F5" s="12">
+        <f>E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="10">
+        <f>C5+(E5*11)</f>
+        <v/>
+      </c>
+      <c r="H5" s="10">
+        <f>B5+(E5*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>AI Intake Agent  (law_firm)</t>
+        </is>
+      </c>
+      <c r="B6" s="12">
+        <f>'All Services'!E14</f>
+        <v/>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>750</v>
+      </c>
+      <c r="D6" s="12">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="12">
+        <f>'All Services'!F14</f>
+        <v/>
+      </c>
+      <c r="F6" s="12">
+        <f>E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="10">
+        <f>C6+(E6*11)</f>
+        <v/>
+      </c>
+      <c r="H6" s="10">
+        <f>B6+(E6*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>AI Front-Desk Agent  (medical)</t>
+        </is>
+      </c>
+      <c r="B7" s="12">
+        <f>'All Services'!E15</f>
+        <v/>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>750</v>
+      </c>
+      <c r="D7" s="12">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="12">
+        <f>'All Services'!F15</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="10">
+        <f>C7+(E7*11)</f>
+        <v/>
+      </c>
+      <c r="H7" s="10">
+        <f>B7+(E7*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Instant Lead Callback  (home_services)</t>
+        </is>
+      </c>
+      <c r="B8" s="12">
+        <f>'All Services'!E16</f>
+        <v/>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D8" s="12">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="12">
+        <f>'All Services'!F16</f>
+        <v/>
+      </c>
+      <c r="F8" s="12">
+        <f>E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="10">
+        <f>C8+(E8*11)</f>
+        <v/>
+      </c>
+      <c r="H8" s="10">
+        <f>B8+(E8*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Instant Lead Callback  (law_firm)</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>'All Services'!E17</f>
+        <v/>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="D9" s="12">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="12">
+        <f>'All Services'!F17</f>
+        <v/>
+      </c>
+      <c r="F9" s="12">
+        <f>E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="10">
+        <f>C9+(E9*11)</f>
+        <v/>
+      </c>
+      <c r="H9" s="10">
+        <f>B9+(E9*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>After-Hours Answering  (home_services, law_firm, medical)</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
+        <f>'All Services'!E18</f>
+        <v/>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D10" s="12">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="12">
+        <f>'All Services'!F18</f>
+        <v/>
+      </c>
+      <c r="F10" s="12">
+        <f>E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="10">
+        <f>C10+(E10*11)</f>
+        <v/>
+      </c>
+      <c r="H10" s="10">
+        <f>B10+(E10*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Spanish-Speaking Agent  (home_services, law_firm, medical)</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
+        <f>'All Services'!E19</f>
+        <v/>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D11" s="12">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="12">
+        <f>'All Services'!F19</f>
+        <v/>
+      </c>
+      <c r="F11" s="12">
+        <f>E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="10">
+        <f>C11+(E11*11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="10">
+        <f>B11+(E11*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Review Requests  (home_services, law_firm)</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>'All Services'!E20</f>
+        <v/>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D12" s="12">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="12">
+        <f>'All Services'!F20</f>
+        <v/>
+      </c>
+      <c r="F12" s="12">
+        <f>E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="10">
+        <f>C12+(E12*11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="10">
+        <f>B12+(E12*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Missed-Call Text-Back  (home_services)</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>'All Services'!E21</f>
+        <v/>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D13" s="12">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="12">
+        <f>'All Services'!F21</f>
+        <v/>
+      </c>
+      <c r="F13" s="12">
+        <f>E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="10">
+        <f>C13+(E13*11)</f>
+        <v/>
+      </c>
+      <c r="H13" s="10">
+        <f>B13+(E13*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Missed-Call Text-Back  (law_firm)</t>
+        </is>
+      </c>
+      <c r="B14" s="12">
+        <f>'All Services'!E22</f>
+        <v/>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="D14" s="12">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="12">
+        <f>'All Services'!F22</f>
+        <v/>
+      </c>
+      <c r="F14" s="12">
+        <f>E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="10">
+        <f>C14+(E14*11)</f>
+        <v/>
+      </c>
+      <c r="H14" s="10">
+        <f>B14+(E14*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Missed-Call Text-Back  (medical)</t>
+        </is>
+      </c>
+      <c r="B15" s="12">
+        <f>'All Services'!E23</f>
+        <v/>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="D15" s="12">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="12">
+        <f>'All Services'!F23</f>
+        <v/>
+      </c>
+      <c r="F15" s="12">
+        <f>E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="10">
+        <f>C15+(E15*11)</f>
+        <v/>
+      </c>
+      <c r="H15" s="10">
+        <f>B15+(E15*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>After-Hours Intake  (home_services)</t>
+        </is>
+      </c>
+      <c r="B16" s="12">
+        <f>'All Services'!E24</f>
+        <v/>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D16" s="12">
+        <f>B16-C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="12">
+        <f>'All Services'!F24</f>
+        <v/>
+      </c>
+      <c r="F16" s="12">
+        <f>E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="10">
+        <f>C16+(E16*11)</f>
+        <v/>
+      </c>
+      <c r="H16" s="10">
+        <f>B16+(E16*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>After-Hours Intake  (law_firm)</t>
+        </is>
+      </c>
+      <c r="B17" s="12">
+        <f>'All Services'!E25</f>
+        <v/>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="D17" s="12">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="12">
+        <f>'All Services'!F25</f>
+        <v/>
+      </c>
+      <c r="F17" s="12">
+        <f>E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="10">
+        <f>C17+(E17*11)</f>
+        <v/>
+      </c>
+      <c r="H17" s="10">
+        <f>B17+(E17*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>After-Hours Intake  (medical)</t>
+        </is>
+      </c>
+      <c r="B18" s="12">
+        <f>'All Services'!E26</f>
+        <v/>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="D18" s="12">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
+        <f>'All Services'!F26</f>
+        <v/>
+      </c>
+      <c r="F18" s="12">
+        <f>E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="10">
+        <f>C18+(E18*11)</f>
+        <v/>
+      </c>
+      <c r="H18" s="10">
+        <f>B18+(E18*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Lead Nurture Sequences  (home_services)</t>
+        </is>
+      </c>
+      <c r="B19" s="12">
+        <f>'All Services'!E27</f>
+        <v/>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D19" s="12">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="12">
+        <f>'All Services'!F27</f>
+        <v/>
+      </c>
+      <c r="F19" s="12">
+        <f>E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="10">
+        <f>C19+(E19*11)</f>
+        <v/>
+      </c>
+      <c r="H19" s="10">
+        <f>B19+(E19*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Lead Nurture Sequences  (law_firm)</t>
+        </is>
+      </c>
+      <c r="B20" s="12">
+        <f>'All Services'!E28</f>
+        <v/>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="D20" s="12">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="12">
+        <f>'All Services'!F28</f>
+        <v/>
+      </c>
+      <c r="F20" s="12">
+        <f>E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="10">
+        <f>C20+(E20*11)</f>
+        <v/>
+      </c>
+      <c r="H20" s="10">
+        <f>B20+(E20*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Recall &amp; Reactivation  (medical)</t>
+        </is>
+      </c>
+      <c r="B21" s="12">
+        <f>'All Services'!E29</f>
+        <v/>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D21" s="12">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="12">
+        <f>'All Services'!F29</f>
+        <v/>
+      </c>
+      <c r="F21" s="12">
+        <f>E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="10">
+        <f>C21+(E21*11)</f>
+        <v/>
+      </c>
+      <c r="H21" s="10">
+        <f>B21+(E21*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Reminders &amp; No-Show Recovery  (home_services)</t>
+        </is>
+      </c>
+      <c r="B22" s="12">
+        <f>'All Services'!E30</f>
+        <v/>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D22" s="12">
+        <f>B22-C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="12">
+        <f>'All Services'!F30</f>
+        <v/>
+      </c>
+      <c r="F22" s="12">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="10">
+        <f>C22+(E22*11)</f>
+        <v/>
+      </c>
+      <c r="H22" s="10">
+        <f>B22+(E22*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Reminders &amp; No-Show Recovery  (law_firm)</t>
+        </is>
+      </c>
+      <c r="B23" s="12">
+        <f>'All Services'!E31</f>
+        <v/>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="D23" s="12">
+        <f>B23-C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="12">
+        <f>'All Services'!F31</f>
+        <v/>
+      </c>
+      <c r="F23" s="12">
+        <f>E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="10">
+        <f>C23+(E23*11)</f>
+        <v/>
+      </c>
+      <c r="H23" s="10">
+        <f>B23+(E23*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Reminders &amp; No-Show Recovery  (medical)</t>
+        </is>
+      </c>
+      <c r="B24" s="12">
+        <f>'All Services'!E32</f>
+        <v/>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D24" s="12">
+        <f>B24-C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="12">
+        <f>'All Services'!F32</f>
+        <v/>
+      </c>
+      <c r="F24" s="12">
+        <f>E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="10">
+        <f>C24+(E24*11)</f>
+        <v/>
+      </c>
+      <c r="H24" s="10">
+        <f>B24+(E24*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Total across every service offered on trial</t>
+        </is>
+      </c>
+      <c r="D25" s="10">
+        <f>SUM(D5:D24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>SUM(F5:F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="10">
+        <f>SUM(G5:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="10">
+        <f>SUM(H5:H24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="46" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>'Given up at signup' is setup discount only. 'Free month costs' is one month's fee forgone — not what it costs to serve, which is far less: a voice minute runs $0.13-0.18 and a text $0.011, so a free month of a $250 service costs well under $10 to actually deliver. The real cost of the offer is the deferred revenue, not the compute.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sanaku/docs/sanaku-services.xlsx
+++ b/sanaku/docs/sanaku-services.xlsx
@@ -676,7 +676,7 @@
         <v>0.45</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="4" t="inlineStr">
@@ -724,7 +724,7 @@
         <v>0.55</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
         <v>0.45</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="inlineStr">
@@ -870,7 +870,7 @@
         <v>0.55</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="inlineStr">
@@ -918,7 +918,7 @@
         <v>0.05</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4" t="inlineStr">
@@ -966,7 +966,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="4" t="inlineStr">
@@ -1110,7 +1110,7 @@
         <v>0.55</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="4" t="inlineStr">
@@ -1208,7 +1208,7 @@
         <v>0.45</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="4" t="inlineStr">
@@ -1256,7 +1256,7 @@
         <v>0.55</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="4" t="inlineStr">
@@ -1434,7 +1434,7 @@
         <v>0.05</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="4" t="inlineStr">
@@ -1482,7 +1482,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="4" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="I24" s="7" t="n"/>
       <c r="J24" s="5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="5" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="4" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="4" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="5" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="4" t="inlineStr">
@@ -5048,7 +5048,7 @@
         <v/>
       </c>
       <c r="C5" s="16" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D5" s="12">
         <f>B5-C5</f>
@@ -5082,7 +5082,7 @@
         <v/>
       </c>
       <c r="C6" s="16" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D6" s="12">
         <f>B6-C6</f>
@@ -5116,7 +5116,7 @@
         <v/>
       </c>
       <c r="C7" s="16" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="D7" s="12">
         <f>B7-C7</f>
@@ -5150,7 +5150,7 @@
         <v/>
       </c>
       <c r="C8" s="16" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="D8" s="12">
         <f>B8-C8</f>
@@ -5218,7 +5218,7 @@
         <v/>
       </c>
       <c r="C10" s="16" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="D10" s="12">
         <f>B10-C10</f>
@@ -5320,7 +5320,7 @@
         <v/>
       </c>
       <c r="C13" s="16" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="D13" s="12">
         <f>B13-C13</f>
@@ -5354,7 +5354,7 @@
         <v/>
       </c>
       <c r="C14" s="16" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="D14" s="12">
         <f>B14-C14</f>
@@ -5388,7 +5388,7 @@
         <v/>
       </c>
       <c r="C15" s="16" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="D15" s="12">
         <f>B15-C15</f>
@@ -5422,7 +5422,7 @@
         <v/>
       </c>
       <c r="C16" s="16" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="D16" s="12">
         <f>B16-C16</f>
@@ -5456,7 +5456,7 @@
         <v/>
       </c>
       <c r="C17" s="16" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D17" s="12">
         <f>B17-C17</f>
@@ -5490,7 +5490,7 @@
         <v/>
       </c>
       <c r="C18" s="16" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="D18" s="12">
         <f>B18-C18</f>
@@ -5524,7 +5524,7 @@
         <v/>
       </c>
       <c r="C19" s="16" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="D19" s="12">
         <f>B19-C19</f>
@@ -5558,7 +5558,7 @@
         <v/>
       </c>
       <c r="C20" s="16" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="D20" s="12">
         <f>B20-C20</f>
@@ -5592,7 +5592,7 @@
         <v/>
       </c>
       <c r="C21" s="16" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="D21" s="12">
         <f>B21-C21</f>
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="C22" s="16" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="D22" s="12">
         <f>B22-C22</f>
@@ -5660,7 +5660,7 @@
         <v/>
       </c>
       <c r="C23" s="16" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="D23" s="12">
         <f>B23-C23</f>
@@ -5694,7 +5694,7 @@
         <v/>
       </c>
       <c r="C24" s="16" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="D24" s="12">
         <f>B24-C24</f>

--- a/sanaku/docs/sanaku-services.xlsx
+++ b/sanaku/docs/sanaku-services.xlsx
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,7 +125,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4968,7 +4967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4984,14 +4983,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The 30-day trial — cost of the offer, and when it pays back</t>
+          <t>The 30-day free month — what it costs you, and when it pays back</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Trial: pay the starting fee, run it 30 days, then the monthly begins. Packages are excluded on purpose — a free month of a package is thousands per prospect.</t>
+          <t>Pay the service's setup fee, run it 30 days, then the monthly begins. There is no trial discount — the free month is the offer, and it applies to every service.</t>
         </is>
       </c>
     </row>
@@ -5003,17 +5002,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Normal setup</t>
+          <t>Setup fee</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Trial start</t>
+          <t>Paid to start</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Given up at signup</t>
+          <t>Discount given</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -5040,22 +5039,23 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>AI Phone Agent  (home_services)</t>
+          <t>The Whole System  (home_services)</t>
         </is>
       </c>
       <c r="B5" s="12">
-        <f>'All Services'!E13</f>
-        <v/>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E5</f>
+        <v/>
+      </c>
+      <c r="C5" s="12">
+        <f>'All Services'!E5</f>
+        <v/>
       </c>
       <c r="D5" s="12">
         <f>B5-C5</f>
         <v/>
       </c>
       <c r="E5" s="12">
-        <f>'All Services'!F13</f>
+        <f>'All Services'!F5</f>
         <v/>
       </c>
       <c r="F5" s="12">
@@ -5074,22 +5074,23 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>AI Intake Agent  (law_firm)</t>
+          <t>The Whole System  (law_firm)</t>
         </is>
       </c>
       <c r="B6" s="12">
-        <f>'All Services'!E14</f>
-        <v/>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E6</f>
+        <v/>
+      </c>
+      <c r="C6" s="12">
+        <f>'All Services'!E6</f>
+        <v/>
       </c>
       <c r="D6" s="12">
         <f>B6-C6</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>'All Services'!F14</f>
+        <f>'All Services'!F6</f>
         <v/>
       </c>
       <c r="F6" s="12">
@@ -5108,22 +5109,23 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>AI Front-Desk Agent  (medical)</t>
+          <t>The Whole System  (medical)</t>
         </is>
       </c>
       <c r="B7" s="12">
-        <f>'All Services'!E15</f>
-        <v/>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E7</f>
+        <v/>
+      </c>
+      <c r="C7" s="12">
+        <f>'All Services'!E7</f>
+        <v/>
       </c>
       <c r="D7" s="12">
         <f>B7-C7</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>'All Services'!F15</f>
+        <f>'All Services'!F7</f>
         <v/>
       </c>
       <c r="F7" s="12">
@@ -5142,22 +5144,23 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Instant Lead Callback  (home_services)</t>
+          <t>Complete Phone Cover  (home_services)</t>
         </is>
       </c>
       <c r="B8" s="12">
-        <f>'All Services'!E16</f>
-        <v/>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E8</f>
+        <v/>
+      </c>
+      <c r="C8" s="12">
+        <f>'All Services'!E8</f>
+        <v/>
       </c>
       <c r="D8" s="12">
         <f>B8-C8</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>'All Services'!F16</f>
+        <f>'All Services'!F8</f>
         <v/>
       </c>
       <c r="F8" s="12">
@@ -5176,22 +5179,23 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Instant Lead Callback  (law_firm)</t>
+          <t>Complete Phone Cover  (law_firm)</t>
         </is>
       </c>
       <c r="B9" s="12">
-        <f>'All Services'!E17</f>
-        <v/>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E9</f>
+        <v/>
+      </c>
+      <c r="C9" s="12">
+        <f>'All Services'!E9</f>
+        <v/>
       </c>
       <c r="D9" s="12">
         <f>B9-C9</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>'All Services'!F17</f>
+        <f>'All Services'!F9</f>
         <v/>
       </c>
       <c r="F9" s="12">
@@ -5210,22 +5214,23 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>After-Hours Answering  (home_services, law_firm, medical)</t>
+          <t>Complete Lead Recovery  (home_services)</t>
         </is>
       </c>
       <c r="B10" s="12">
-        <f>'All Services'!E18</f>
-        <v/>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>350</v>
+        <f>'All Services'!E10</f>
+        <v/>
+      </c>
+      <c r="C10" s="12">
+        <f>'All Services'!E10</f>
+        <v/>
       </c>
       <c r="D10" s="12">
         <f>B10-C10</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>'All Services'!F18</f>
+        <f>'All Services'!F10</f>
         <v/>
       </c>
       <c r="F10" s="12">
@@ -5244,22 +5249,23 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Spanish-Speaking Agent  (home_services, law_firm, medical)</t>
+          <t>Complete Lead Recovery  (law_firm)</t>
         </is>
       </c>
       <c r="B11" s="12">
-        <f>'All Services'!E19</f>
-        <v/>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>250</v>
+        <f>'All Services'!E11</f>
+        <v/>
+      </c>
+      <c r="C11" s="12">
+        <f>'All Services'!E11</f>
+        <v/>
       </c>
       <c r="D11" s="12">
         <f>B11-C11</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>'All Services'!F19</f>
+        <f>'All Services'!F11</f>
         <v/>
       </c>
       <c r="F11" s="12">
@@ -5278,22 +5284,23 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Review Requests  (home_services, law_firm)</t>
+          <t>Complete Lead Recovery  (medical)</t>
         </is>
       </c>
       <c r="B12" s="12">
-        <f>'All Services'!E20</f>
-        <v/>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>250</v>
+        <f>'All Services'!E12</f>
+        <v/>
+      </c>
+      <c r="C12" s="12">
+        <f>'All Services'!E12</f>
+        <v/>
       </c>
       <c r="D12" s="12">
         <f>B12-C12</f>
         <v/>
       </c>
       <c r="E12" s="12">
-        <f>'All Services'!F20</f>
+        <f>'All Services'!F12</f>
         <v/>
       </c>
       <c r="F12" s="12">
@@ -5312,22 +5319,23 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Missed-Call Text-Back  (home_services)</t>
+          <t>AI Phone Agent  (home_services)</t>
         </is>
       </c>
       <c r="B13" s="12">
-        <f>'All Services'!E21</f>
-        <v/>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E13</f>
+        <v/>
+      </c>
+      <c r="C13" s="12">
+        <f>'All Services'!E13</f>
+        <v/>
       </c>
       <c r="D13" s="12">
         <f>B13-C13</f>
         <v/>
       </c>
       <c r="E13" s="12">
-        <f>'All Services'!F21</f>
+        <f>'All Services'!F13</f>
         <v/>
       </c>
       <c r="F13" s="12">
@@ -5346,22 +5354,23 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Missed-Call Text-Back  (law_firm)</t>
+          <t>AI Intake Agent  (law_firm)</t>
         </is>
       </c>
       <c r="B14" s="12">
-        <f>'All Services'!E22</f>
-        <v/>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E14</f>
+        <v/>
+      </c>
+      <c r="C14" s="12">
+        <f>'All Services'!E14</f>
+        <v/>
       </c>
       <c r="D14" s="12">
         <f>B14-C14</f>
         <v/>
       </c>
       <c r="E14" s="12">
-        <f>'All Services'!F22</f>
+        <f>'All Services'!F14</f>
         <v/>
       </c>
       <c r="F14" s="12">
@@ -5380,22 +5389,23 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Missed-Call Text-Back  (medical)</t>
+          <t>AI Front-Desk Agent  (medical)</t>
         </is>
       </c>
       <c r="B15" s="12">
-        <f>'All Services'!E23</f>
-        <v/>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E15</f>
+        <v/>
+      </c>
+      <c r="C15" s="12">
+        <f>'All Services'!E15</f>
+        <v/>
       </c>
       <c r="D15" s="12">
         <f>B15-C15</f>
         <v/>
       </c>
       <c r="E15" s="12">
-        <f>'All Services'!F23</f>
+        <f>'All Services'!F15</f>
         <v/>
       </c>
       <c r="F15" s="12">
@@ -5414,22 +5424,23 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>After-Hours Intake  (home_services)</t>
+          <t>Instant Lead Callback  (home_services)</t>
         </is>
       </c>
       <c r="B16" s="12">
-        <f>'All Services'!E24</f>
-        <v/>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>400</v>
+        <f>'All Services'!E16</f>
+        <v/>
+      </c>
+      <c r="C16" s="12">
+        <f>'All Services'!E16</f>
+        <v/>
       </c>
       <c r="D16" s="12">
         <f>B16-C16</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>'All Services'!F24</f>
+        <f>'All Services'!F16</f>
         <v/>
       </c>
       <c r="F16" s="12">
@@ -5448,22 +5459,23 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>After-Hours Intake  (law_firm)</t>
+          <t>Instant Lead Callback  (law_firm)</t>
         </is>
       </c>
       <c r="B17" s="12">
-        <f>'All Services'!E25</f>
-        <v/>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E17</f>
+        <v/>
+      </c>
+      <c r="C17" s="12">
+        <f>'All Services'!E17</f>
+        <v/>
       </c>
       <c r="D17" s="12">
         <f>B17-C17</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>'All Services'!F25</f>
+        <f>'All Services'!F17</f>
         <v/>
       </c>
       <c r="F17" s="12">
@@ -5482,22 +5494,23 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>After-Hours Intake  (medical)</t>
+          <t>After-Hours Answering  (home_services, law_firm, medical)</t>
         </is>
       </c>
       <c r="B18" s="12">
-        <f>'All Services'!E26</f>
-        <v/>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E18</f>
+        <v/>
+      </c>
+      <c r="C18" s="12">
+        <f>'All Services'!E18</f>
+        <v/>
       </c>
       <c r="D18" s="12">
         <f>B18-C18</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>'All Services'!F26</f>
+        <f>'All Services'!F18</f>
         <v/>
       </c>
       <c r="F18" s="12">
@@ -5516,22 +5529,23 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Lead Nurture Sequences  (home_services)</t>
+          <t>Spanish-Speaking Agent  (home_services, law_firm, medical)</t>
         </is>
       </c>
       <c r="B19" s="12">
-        <f>'All Services'!E27</f>
-        <v/>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E19</f>
+        <v/>
+      </c>
+      <c r="C19" s="12">
+        <f>'All Services'!E19</f>
+        <v/>
       </c>
       <c r="D19" s="12">
         <f>B19-C19</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>'All Services'!F27</f>
+        <f>'All Services'!F19</f>
         <v/>
       </c>
       <c r="F19" s="12">
@@ -5550,22 +5564,23 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Lead Nurture Sequences  (law_firm)</t>
+          <t>Review Requests  (home_services, law_firm)</t>
         </is>
       </c>
       <c r="B20" s="12">
-        <f>'All Services'!E28</f>
-        <v/>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E20</f>
+        <v/>
+      </c>
+      <c r="C20" s="12">
+        <f>'All Services'!E20</f>
+        <v/>
       </c>
       <c r="D20" s="12">
         <f>B20-C20</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>'All Services'!F28</f>
+        <f>'All Services'!F20</f>
         <v/>
       </c>
       <c r="F20" s="12">
@@ -5584,22 +5599,23 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Recall &amp; Reactivation  (medical)</t>
+          <t>Missed-Call Text-Back  (home_services)</t>
         </is>
       </c>
       <c r="B21" s="12">
-        <f>'All Services'!E29</f>
-        <v/>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E21</f>
+        <v/>
+      </c>
+      <c r="C21" s="12">
+        <f>'All Services'!E21</f>
+        <v/>
       </c>
       <c r="D21" s="12">
         <f>B21-C21</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>'All Services'!F29</f>
+        <f>'All Services'!F21</f>
         <v/>
       </c>
       <c r="F21" s="12">
@@ -5618,22 +5634,23 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Reminders &amp; No-Show Recovery  (home_services)</t>
+          <t>Missed-Call Text-Back  (law_firm)</t>
         </is>
       </c>
       <c r="B22" s="12">
-        <f>'All Services'!E30</f>
-        <v/>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>350</v>
+        <f>'All Services'!E22</f>
+        <v/>
+      </c>
+      <c r="C22" s="12">
+        <f>'All Services'!E22</f>
+        <v/>
       </c>
       <c r="D22" s="12">
         <f>B22-C22</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>'All Services'!F30</f>
+        <f>'All Services'!F22</f>
         <v/>
       </c>
       <c r="F22" s="12">
@@ -5652,22 +5669,23 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Reminders &amp; No-Show Recovery  (law_firm)</t>
+          <t>Missed-Call Text-Back  (medical)</t>
         </is>
       </c>
       <c r="B23" s="12">
-        <f>'All Services'!E31</f>
-        <v/>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>500</v>
+        <f>'All Services'!E23</f>
+        <v/>
+      </c>
+      <c r="C23" s="12">
+        <f>'All Services'!E23</f>
+        <v/>
       </c>
       <c r="D23" s="12">
         <f>B23-C23</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>'All Services'!F31</f>
+        <f>'All Services'!F23</f>
         <v/>
       </c>
       <c r="F23" s="12">
@@ -5686,22 +5704,23 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Reminders &amp; No-Show Recovery  (medical)</t>
+          <t>After-Hours Intake  (home_services)</t>
         </is>
       </c>
       <c r="B24" s="12">
-        <f>'All Services'!E32</f>
-        <v/>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>450</v>
+        <f>'All Services'!E24</f>
+        <v/>
+      </c>
+      <c r="C24" s="12">
+        <f>'All Services'!E24</f>
+        <v/>
       </c>
       <c r="D24" s="12">
         <f>B24-C24</f>
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>'All Services'!F32</f>
+        <f>'All Services'!F24</f>
         <v/>
       </c>
       <c r="F24" s="12">
@@ -5718,30 +5737,310 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>After-Hours Intake  (law_firm)</t>
+        </is>
+      </c>
+      <c r="B25" s="12">
+        <f>'All Services'!E25</f>
+        <v/>
+      </c>
+      <c r="C25" s="12">
+        <f>'All Services'!E25</f>
+        <v/>
+      </c>
+      <c r="D25" s="12">
+        <f>B25-C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="12">
+        <f>'All Services'!F25</f>
+        <v/>
+      </c>
+      <c r="F25" s="12">
+        <f>E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="10">
+        <f>C25+(E25*11)</f>
+        <v/>
+      </c>
+      <c r="H25" s="10">
+        <f>B25+(E25*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>After-Hours Intake  (medical)</t>
+        </is>
+      </c>
+      <c r="B26" s="12">
+        <f>'All Services'!E26</f>
+        <v/>
+      </c>
+      <c r="C26" s="12">
+        <f>'All Services'!E26</f>
+        <v/>
+      </c>
+      <c r="D26" s="12">
+        <f>B26-C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="12">
+        <f>'All Services'!F26</f>
+        <v/>
+      </c>
+      <c r="F26" s="12">
+        <f>E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="10">
+        <f>C26+(E26*11)</f>
+        <v/>
+      </c>
+      <c r="H26" s="10">
+        <f>B26+(E26*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Lead Nurture Sequences  (home_services)</t>
+        </is>
+      </c>
+      <c r="B27" s="12">
+        <f>'All Services'!E27</f>
+        <v/>
+      </c>
+      <c r="C27" s="12">
+        <f>'All Services'!E27</f>
+        <v/>
+      </c>
+      <c r="D27" s="12">
+        <f>B27-C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="12">
+        <f>'All Services'!F27</f>
+        <v/>
+      </c>
+      <c r="F27" s="12">
+        <f>E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="10">
+        <f>C27+(E27*11)</f>
+        <v/>
+      </c>
+      <c r="H27" s="10">
+        <f>B27+(E27*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Lead Nurture Sequences  (law_firm)</t>
+        </is>
+      </c>
+      <c r="B28" s="12">
+        <f>'All Services'!E28</f>
+        <v/>
+      </c>
+      <c r="C28" s="12">
+        <f>'All Services'!E28</f>
+        <v/>
+      </c>
+      <c r="D28" s="12">
+        <f>B28-C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="12">
+        <f>'All Services'!F28</f>
+        <v/>
+      </c>
+      <c r="F28" s="12">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="10">
+        <f>C28+(E28*11)</f>
+        <v/>
+      </c>
+      <c r="H28" s="10">
+        <f>B28+(E28*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Recall &amp; Reactivation  (medical)</t>
+        </is>
+      </c>
+      <c r="B29" s="12">
+        <f>'All Services'!E29</f>
+        <v/>
+      </c>
+      <c r="C29" s="12">
+        <f>'All Services'!E29</f>
+        <v/>
+      </c>
+      <c r="D29" s="12">
+        <f>B29-C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="12">
+        <f>'All Services'!F29</f>
+        <v/>
+      </c>
+      <c r="F29" s="12">
+        <f>E29</f>
+        <v/>
+      </c>
+      <c r="G29" s="10">
+        <f>C29+(E29*11)</f>
+        <v/>
+      </c>
+      <c r="H29" s="10">
+        <f>B29+(E29*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Reminders &amp; No-Show Recovery  (home_services)</t>
+        </is>
+      </c>
+      <c r="B30" s="12">
+        <f>'All Services'!E30</f>
+        <v/>
+      </c>
+      <c r="C30" s="12">
+        <f>'All Services'!E30</f>
+        <v/>
+      </c>
+      <c r="D30" s="12">
+        <f>B30-C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="12">
+        <f>'All Services'!F30</f>
+        <v/>
+      </c>
+      <c r="F30" s="12">
+        <f>E30</f>
+        <v/>
+      </c>
+      <c r="G30" s="10">
+        <f>C30+(E30*11)</f>
+        <v/>
+      </c>
+      <c r="H30" s="10">
+        <f>B30+(E30*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Reminders &amp; No-Show Recovery  (law_firm)</t>
+        </is>
+      </c>
+      <c r="B31" s="12">
+        <f>'All Services'!E31</f>
+        <v/>
+      </c>
+      <c r="C31" s="12">
+        <f>'All Services'!E31</f>
+        <v/>
+      </c>
+      <c r="D31" s="12">
+        <f>B31-C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="12">
+        <f>'All Services'!F31</f>
+        <v/>
+      </c>
+      <c r="F31" s="12">
+        <f>E31</f>
+        <v/>
+      </c>
+      <c r="G31" s="10">
+        <f>C31+(E31*11)</f>
+        <v/>
+      </c>
+      <c r="H31" s="10">
+        <f>B31+(E31*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Reminders &amp; No-Show Recovery  (medical)</t>
+        </is>
+      </c>
+      <c r="B32" s="12">
+        <f>'All Services'!E32</f>
+        <v/>
+      </c>
+      <c r="C32" s="12">
+        <f>'All Services'!E32</f>
+        <v/>
+      </c>
+      <c r="D32" s="12">
+        <f>B32-C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="12">
+        <f>'All Services'!F32</f>
+        <v/>
+      </c>
+      <c r="F32" s="12">
+        <f>E32</f>
+        <v/>
+      </c>
+      <c r="G32" s="10">
+        <f>C32+(E32*11)</f>
+        <v/>
+      </c>
+      <c r="H32" s="10">
+        <f>B32+(E32*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Total across every service offered on trial</t>
         </is>
       </c>
-      <c r="D25" s="10">
-        <f>SUM(D5:D24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="10">
-        <f>SUM(F5:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="10">
-        <f>SUM(G5:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="10">
-        <f>SUM(H5:H24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="46" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="D33" s="10">
+        <f>SUM(D5:D32)</f>
+        <v/>
+      </c>
+      <c r="F33" s="10">
+        <f>SUM(F5:F32)</f>
+        <v/>
+      </c>
+      <c r="G33" s="10">
+        <f>SUM(G5:G32)</f>
+        <v/>
+      </c>
+      <c r="H33" s="10">
+        <f>SUM(H5:H32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="46" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>'Given up at signup' is setup discount only. 'Free month costs' is one month's fee forgone — not what it costs to serve, which is far less: a voice minute runs $0.13-0.18 and a text $0.011, so a free month of a $250 service costs well under $10 to actually deliver. The real cost of the offer is the deferred revenue, not the compute.</t>
         </is>
@@ -5749,8 +6048,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A35:H35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sanaku/docs/sanaku-services.xlsx
+++ b/sanaku/docs/sanaku-services.xlsx
@@ -4990,7 +4990,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pay the service's setup fee, run it 30 days, then the monthly begins. There is no trial discount — the free month is the offer, and it applies to every service.</t>
+          <t>Pay at most $750 to start, run it 30 days, then the monthly begins and the balance of setup falls due — only if they continue. Nothing here is discounted: the free month and the deferred balance are the offer.</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Discount given</t>
+          <t>Balance at day 31</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -5047,7 +5047,7 @@
         <v/>
       </c>
       <c r="C5" s="12">
-        <f>'All Services'!E5</f>
+        <f>MIN('All Services'!E5,750)</f>
         <v/>
       </c>
       <c r="D5" s="12">
@@ -5082,7 +5082,7 @@
         <v/>
       </c>
       <c r="C6" s="12">
-        <f>'All Services'!E6</f>
+        <f>MIN('All Services'!E6,750)</f>
         <v/>
       </c>
       <c r="D6" s="12">
@@ -5117,7 +5117,7 @@
         <v/>
       </c>
       <c r="C7" s="12">
-        <f>'All Services'!E7</f>
+        <f>MIN('All Services'!E7,750)</f>
         <v/>
       </c>
       <c r="D7" s="12">
@@ -5152,7 +5152,7 @@
         <v/>
       </c>
       <c r="C8" s="12">
-        <f>'All Services'!E8</f>
+        <f>MIN('All Services'!E8,750)</f>
         <v/>
       </c>
       <c r="D8" s="12">
@@ -5187,7 +5187,7 @@
         <v/>
       </c>
       <c r="C9" s="12">
-        <f>'All Services'!E9</f>
+        <f>MIN('All Services'!E9,750)</f>
         <v/>
       </c>
       <c r="D9" s="12">
@@ -5222,7 +5222,7 @@
         <v/>
       </c>
       <c r="C10" s="12">
-        <f>'All Services'!E10</f>
+        <f>MIN('All Services'!E10,750)</f>
         <v/>
       </c>
       <c r="D10" s="12">
@@ -5257,7 +5257,7 @@
         <v/>
       </c>
       <c r="C11" s="12">
-        <f>'All Services'!E11</f>
+        <f>MIN('All Services'!E11,750)</f>
         <v/>
       </c>
       <c r="D11" s="12">
@@ -5292,7 +5292,7 @@
         <v/>
       </c>
       <c r="C12" s="12">
-        <f>'All Services'!E12</f>
+        <f>MIN('All Services'!E12,750)</f>
         <v/>
       </c>
       <c r="D12" s="12">
@@ -5327,7 +5327,7 @@
         <v/>
       </c>
       <c r="C13" s="12">
-        <f>'All Services'!E13</f>
+        <f>MIN('All Services'!E13,750)</f>
         <v/>
       </c>
       <c r="D13" s="12">
@@ -5362,7 +5362,7 @@
         <v/>
       </c>
       <c r="C14" s="12">
-        <f>'All Services'!E14</f>
+        <f>MIN('All Services'!E14,750)</f>
         <v/>
       </c>
       <c r="D14" s="12">
@@ -5397,7 +5397,7 @@
         <v/>
       </c>
       <c r="C15" s="12">
-        <f>'All Services'!E15</f>
+        <f>MIN('All Services'!E15,750)</f>
         <v/>
       </c>
       <c r="D15" s="12">
@@ -5432,7 +5432,7 @@
         <v/>
       </c>
       <c r="C16" s="12">
-        <f>'All Services'!E16</f>
+        <f>MIN('All Services'!E16,750)</f>
         <v/>
       </c>
       <c r="D16" s="12">
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="C17" s="12">
-        <f>'All Services'!E17</f>
+        <f>MIN('All Services'!E17,750)</f>
         <v/>
       </c>
       <c r="D17" s="12">
@@ -5502,7 +5502,7 @@
         <v/>
       </c>
       <c r="C18" s="12">
-        <f>'All Services'!E18</f>
+        <f>MIN('All Services'!E18,750)</f>
         <v/>
       </c>
       <c r="D18" s="12">
@@ -5537,7 +5537,7 @@
         <v/>
       </c>
       <c r="C19" s="12">
-        <f>'All Services'!E19</f>
+        <f>MIN('All Services'!E19,750)</f>
         <v/>
       </c>
       <c r="D19" s="12">
@@ -5572,7 +5572,7 @@
         <v/>
       </c>
       <c r="C20" s="12">
-        <f>'All Services'!E20</f>
+        <f>MIN('All Services'!E20,750)</f>
         <v/>
       </c>
       <c r="D20" s="12">
@@ -5607,7 +5607,7 @@
         <v/>
       </c>
       <c r="C21" s="12">
-        <f>'All Services'!E21</f>
+        <f>MIN('All Services'!E21,750)</f>
         <v/>
       </c>
       <c r="D21" s="12">
@@ -5642,7 +5642,7 @@
         <v/>
       </c>
       <c r="C22" s="12">
-        <f>'All Services'!E22</f>
+        <f>MIN('All Services'!E22,750)</f>
         <v/>
       </c>
       <c r="D22" s="12">
@@ -5677,7 +5677,7 @@
         <v/>
       </c>
       <c r="C23" s="12">
-        <f>'All Services'!E23</f>
+        <f>MIN('All Services'!E23,750)</f>
         <v/>
       </c>
       <c r="D23" s="12">
@@ -5712,7 +5712,7 @@
         <v/>
       </c>
       <c r="C24" s="12">
-        <f>'All Services'!E24</f>
+        <f>MIN('All Services'!E24,750)</f>
         <v/>
       </c>
       <c r="D24" s="12">
@@ -5747,7 +5747,7 @@
         <v/>
       </c>
       <c r="C25" s="12">
-        <f>'All Services'!E25</f>
+        <f>MIN('All Services'!E25,750)</f>
         <v/>
       </c>
       <c r="D25" s="12">
@@ -5782,7 +5782,7 @@
         <v/>
       </c>
       <c r="C26" s="12">
-        <f>'All Services'!E26</f>
+        <f>MIN('All Services'!E26,750)</f>
         <v/>
       </c>
       <c r="D26" s="12">
@@ -5817,7 +5817,7 @@
         <v/>
       </c>
       <c r="C27" s="12">
-        <f>'All Services'!E27</f>
+        <f>MIN('All Services'!E27,750)</f>
         <v/>
       </c>
       <c r="D27" s="12">
@@ -5852,7 +5852,7 @@
         <v/>
       </c>
       <c r="C28" s="12">
-        <f>'All Services'!E28</f>
+        <f>MIN('All Services'!E28,750)</f>
         <v/>
       </c>
       <c r="D28" s="12">
@@ -5887,7 +5887,7 @@
         <v/>
       </c>
       <c r="C29" s="12">
-        <f>'All Services'!E29</f>
+        <f>MIN('All Services'!E29,750)</f>
         <v/>
       </c>
       <c r="D29" s="12">
@@ -5922,7 +5922,7 @@
         <v/>
       </c>
       <c r="C30" s="12">
-        <f>'All Services'!E30</f>
+        <f>MIN('All Services'!E30,750)</f>
         <v/>
       </c>
       <c r="D30" s="12">
@@ -5957,7 +5957,7 @@
         <v/>
       </c>
       <c r="C31" s="12">
-        <f>'All Services'!E31</f>
+        <f>MIN('All Services'!E31,750)</f>
         <v/>
       </c>
       <c r="D31" s="12">
@@ -5992,7 +5992,7 @@
         <v/>
       </c>
       <c r="C32" s="12">
-        <f>'All Services'!E32</f>
+        <f>MIN('All Services'!E32,750)</f>
         <v/>
       </c>
       <c r="D32" s="12">
@@ -6042,7 +6042,7 @@
     <row r="35" ht="46" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>'Given up at signup' is setup discount only. 'Free month costs' is one month's fee forgone — not what it costs to serve, which is far less: a voice minute runs $0.13-0.18 and a text $0.011, so a free month of a $250 service costs well under $10 to actually deliver. The real cost of the offer is the deferred revenue, not the compute.</t>
+          <t>'Balance at day 31' is deferred, not discounted - billed in full if they continue and written off only if they walk. 'Free month costs' is one month's fee forgone — not what it costs to serve, which is far less: a voice minute runs $0.13-0.18 and a text $0.011, so a free month of a $250 service costs well under $10 to actually deliver. The real cost of the offer is the deferred revenue, not the compute.</t>
         </is>
       </c>
     </row>
